--- a/exports/trend_1d/PIDILITIND_full_report.xlsx
+++ b/exports/trend_1d/PIDILITIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.42</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42117</v>
+        <v>42118</v>
       </c>
       <c r="H2" t="n">
-        <v>285.9</v>
+        <v>280</v>
       </c>
       <c r="I2" t="n">
         <v>282.2177871254773</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.42</v>
+        <v>-4.44</v>
       </c>
       <c r="L2" t="n">
         <v>9.9</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42139</v>
+        <v>42142</v>
       </c>
       <c r="H3" t="n">
-        <v>297.8</v>
+        <v>299.6</v>
       </c>
       <c r="I3" t="n">
         <v>299.3403783725744</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.36</v>
+        <v>-7</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>8.93</v>
       </c>
       <c r="M3" t="n">
         <v>0.53</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42156</v>
+        <v>42157</v>
       </c>
       <c r="H4" t="n">
-        <v>277</v>
+        <v>273.5</v>
       </c>
       <c r="I4" t="n">
         <v>273.5706746743228</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.54</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>10.68</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>10.05</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42219</v>
+        <v>42220</v>
       </c>
       <c r="H5" t="n">
-        <v>276.8</v>
+        <v>295.9</v>
       </c>
       <c r="I5" t="n">
         <v>288.3597462987354</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.21</v>
+        <v>-8.19</v>
       </c>
       <c r="L5" t="n">
-        <v>5.67</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>4.21</v>
       </c>
       <c r="N5" t="n">
-        <v>4.74</v>
+        <v>6.9</v>
       </c>
       <c r="O5" t="n">
         <v>-1.26</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>11.4</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>282.7</v>
+        <v>274.4</v>
       </c>
       <c r="I6" t="n">
         <v>275.5989452485384</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.46</v>
+        <v>-7.27</v>
       </c>
       <c r="L6" t="n">
-        <v>6.93</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.46</v>
+        <v>4.39</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
         <v>6.9</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.58</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42373</v>
+        <v>42374</v>
       </c>
       <c r="H7" t="n">
-        <v>278.8</v>
+        <v>283.8</v>
       </c>
       <c r="I7" t="n">
         <v>282.5857928153993</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6</v>
+        <v>-3.43</v>
       </c>
       <c r="L7" t="n">
         <v>7.51</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.59</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42389</v>
+        <v>42390</v>
       </c>
       <c r="H8" t="n">
-        <v>267.4</v>
+        <v>265.1</v>
       </c>
       <c r="I8" t="n">
         <v>267.1370173085667</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.78</v>
+        <v>-6.59</v>
       </c>
       <c r="L8" t="n">
         <v>6.91</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.32</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42403</v>
+        <v>42404</v>
       </c>
       <c r="H9" t="n">
-        <v>283.5</v>
+        <v>291.2</v>
       </c>
       <c r="I9" t="n">
         <v>287.145564796795</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.94</v>
+        <v>-9.85</v>
       </c>
       <c r="L9" t="n">
-        <v>10.49</v>
+        <v>10.6</v>
       </c>
       <c r="M9" t="n">
         <v>2.44</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.81</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42452</v>
+        <v>42457</v>
       </c>
       <c r="H10" t="n">
-        <v>299.9</v>
+        <v>288.8</v>
       </c>
       <c r="I10" t="n">
         <v>290.1169146240807</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K10" t="n">
-        <v>2.99</v>
+        <v>-0.82</v>
       </c>
       <c r="L10" t="n">
-        <v>2.47</v>
+        <v>3.43</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>8.9</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42509</v>
+        <v>42510</v>
       </c>
       <c r="H11" t="n">
-        <v>308.3</v>
+        <v>326.8</v>
       </c>
       <c r="I11" t="n">
         <v>314.4981509220635</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.75</v>
+        <v>-13.16</v>
       </c>
       <c r="L11" t="n">
-        <v>9.73</v>
+        <v>13.71</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.08</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
         <v>-3.7</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.42</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42600</v>
+        <v>42601</v>
       </c>
       <c r="H12" t="n">
-        <v>354.5</v>
+        <v>349.9</v>
       </c>
       <c r="I12" t="n">
         <v>350.8169160285519</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" t="n">
-        <v>8.48</v>
+        <v>7.07</v>
       </c>
       <c r="L12" t="n">
         <v>3.92</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>7.69</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42643</v>
+        <v>42646</v>
       </c>
       <c r="H13" t="n">
-        <v>340.8</v>
+        <v>362.1</v>
       </c>
       <c r="I13" t="n">
         <v>361.6651994210291</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>-3.49</v>
       </c>
       <c r="L13" t="n">
-        <v>3.66</v>
+        <v>3.86</v>
       </c>
       <c r="M13" t="n">
         <v>0.86</v>
       </c>
       <c r="N13" t="n">
-        <v>3.13</v>
+        <v>6.25</v>
       </c>
       <c r="O13" t="n">
         <v>-1.3</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.03</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H14" t="n">
-        <v>339</v>
+        <v>332.8</v>
       </c>
       <c r="I14" t="n">
         <v>338.8567976598628</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.38</v>
+        <v>-8.09</v>
       </c>
       <c r="L14" t="n">
         <v>11.76</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.98</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42744</v>
+        <v>42745</v>
       </c>
       <c r="H15" t="n">
-        <v>307.1</v>
+        <v>315.7</v>
       </c>
       <c r="I15" t="n">
         <v>312.372152470888</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K15" t="n">
-        <v>7.72</v>
+        <v>5.14</v>
       </c>
       <c r="L15" t="n">
         <v>5.02</v>
@@ -1296,7 +1475,7 @@
         <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>-1.83</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.41</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H16" t="n">
-        <v>367.8</v>
+        <v>360.4</v>
       </c>
       <c r="I16" t="n">
         <v>361.7969708363952</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K16" t="n">
-        <v>16.5</v>
+        <v>14.16</v>
       </c>
       <c r="L16" t="n">
         <v>3.52</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42887</v>
+        <v>42888</v>
       </c>
       <c r="H17" t="n">
-        <v>382.8</v>
+        <v>395.8</v>
       </c>
       <c r="I17" t="n">
         <v>391.200389690817</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.22</v>
+        <v>-9.82</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8</v>
+        <v>10.71</v>
       </c>
       <c r="M17" t="n">
         <v>0.88</v>
       </c>
       <c r="N17" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>-2.01</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.07</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H18" t="n">
-        <v>407</v>
+        <v>402.8</v>
       </c>
       <c r="I18" t="n">
         <v>404.5079199364278</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K18" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="L18" t="n">
         <v>3.28</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>6.59</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43047</v>
+        <v>43048</v>
       </c>
       <c r="H19" t="n">
-        <v>384.4</v>
+        <v>406.4</v>
       </c>
       <c r="I19" t="n">
         <v>405.4622200466176</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K19" t="n">
-        <v>4.57</v>
+        <v>-0.89</v>
       </c>
       <c r="L19" t="n">
         <v>1.91</v>
       </c>
       <c r="M19" t="n">
-        <v>0.85</v>
+        <v>2.63</v>
       </c>
       <c r="N19" t="n">
-        <v>2.19</v>
+        <v>5.72</v>
       </c>
       <c r="O19" t="n">
         <v>-1.03</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.02</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43258</v>
+        <v>43259</v>
       </c>
       <c r="H20" t="n">
-        <v>543.7</v>
+        <v>535.2</v>
       </c>
       <c r="I20" t="n">
         <v>536.2646793900215</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K20" t="n">
-        <v>33.78</v>
+        <v>31.69</v>
       </c>
       <c r="L20" t="n">
         <v>3.91</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43305</v>
+        <v>43306</v>
       </c>
       <c r="H21" t="n">
-        <v>538.5</v>
+        <v>558.8</v>
       </c>
       <c r="I21" t="n">
         <v>556.3972480468753</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.62</v>
+        <v>-4.41</v>
       </c>
       <c r="L21" t="n">
-        <v>3.48</v>
+        <v>5.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.42</v>
+        <v>3.77</v>
       </c>
       <c r="O21" t="n">
         <v>-1.56</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.08</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43368</v>
+        <v>43369</v>
       </c>
       <c r="H22" t="n">
-        <v>550.1</v>
+        <v>538</v>
       </c>
       <c r="I22" t="n">
         <v>545.7577129582789</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.56</v>
+        <v>-3.72</v>
       </c>
       <c r="L22" t="n">
-        <v>3.63</v>
+        <v>4.35</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.76</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43416</v>
+        <v>43417</v>
       </c>
       <c r="H23" t="n">
-        <v>513.4</v>
+        <v>531.6</v>
       </c>
       <c r="I23" t="n">
         <v>526.8870281274236</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K23" t="n">
-        <v>4.57</v>
+        <v>1.19</v>
       </c>
       <c r="L23" t="n">
         <v>3.72</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.11</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43510</v>
+        <v>43511</v>
       </c>
       <c r="H24" t="n">
-        <v>556.7</v>
+        <v>548</v>
       </c>
       <c r="I24" t="n">
         <v>548.2009817872325</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="n">
-        <v>4.72</v>
+        <v>3.09</v>
       </c>
       <c r="L24" t="n">
         <v>4.06</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43536</v>
+        <v>43537</v>
       </c>
       <c r="H25" t="n">
-        <v>565.9</v>
+        <v>588.2</v>
       </c>
       <c r="I25" t="n">
         <v>584.8230514181454</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.27</v>
+        <v>-7.34</v>
       </c>
       <c r="L25" t="n">
-        <v>6.72</v>
+        <v>7.85</v>
       </c>
       <c r="M25" t="n">
         <v>0.62</v>
       </c>
       <c r="N25" t="n">
-        <v>2.67</v>
+        <v>3.94</v>
       </c>
       <c r="O25" t="n">
         <v>-1.56</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43577</v>
+        <v>43578</v>
       </c>
       <c r="H26" t="n">
-        <v>615</v>
+        <v>603.4</v>
       </c>
       <c r="I26" t="n">
         <v>611.146956736433</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>4.56</v>
+        <v>2.58</v>
       </c>
       <c r="L26" t="n">
         <v>3.84</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.49</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H27" t="n">
-        <v>599.8</v>
+        <v>618.8</v>
       </c>
       <c r="I27" t="n">
         <v>613.0467936157129</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6</v>
+        <v>-2.55</v>
       </c>
       <c r="L27" t="n">
         <v>3.99</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>10.76</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H28" t="n">
-        <v>603.1</v>
+        <v>599.8</v>
       </c>
       <c r="I28" t="n">
         <v>600.3544087016353</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.54</v>
+        <v>-3.07</v>
       </c>
       <c r="L28" t="n">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="M28" t="n">
         <v>0.83</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.5</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43678</v>
+        <v>43679</v>
       </c>
       <c r="H29" t="n">
-        <v>605.7</v>
+        <v>628.4</v>
       </c>
       <c r="I29" t="n">
         <v>626.3448900802715</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.98</v>
+        <v>-4.77</v>
       </c>
       <c r="L29" t="n">
-        <v>4.53</v>
+        <v>5.82</v>
       </c>
       <c r="M29" t="n">
         <v>0.57</v>
       </c>
       <c r="N29" t="n">
-        <v>2.19</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>-0.55</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.68</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43726</v>
+        <v>43727</v>
       </c>
       <c r="H30" t="n">
-        <v>654.9</v>
+        <v>647.3</v>
       </c>
       <c r="I30" t="n">
         <v>651.0015670514531</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K30" t="n">
-        <v>4.22</v>
+        <v>3.01</v>
       </c>
       <c r="L30" t="n">
         <v>5.63</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>6.89</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H31" t="n">
-        <v>647.3</v>
+        <v>704.4</v>
       </c>
       <c r="I31" t="n">
         <v>691.9260161717875</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>-8.82</v>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>9.84</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="O31" t="n">
         <v>-1.16</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.91</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43745</v>
+        <v>43747</v>
       </c>
       <c r="H32" t="n">
-        <v>683</v>
+        <v>668.3</v>
       </c>
       <c r="I32" t="n">
         <v>672.2954842107669</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.04</v>
+        <v>-5.12</v>
       </c>
       <c r="L32" t="n">
         <v>8.57</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.79</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43823</v>
+        <v>43825</v>
       </c>
       <c r="H33" t="n">
-        <v>688.4</v>
+        <v>695</v>
       </c>
       <c r="I33" t="n">
         <v>693.0206804425643</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.01</v>
+        <v>-4</v>
       </c>
       <c r="L33" t="n">
         <v>6.57</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.13</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43903</v>
+        <v>43906</v>
       </c>
       <c r="H34" t="n">
-        <v>761.9</v>
+        <v>740.3</v>
       </c>
       <c r="I34" t="n">
         <v>753.227548299743</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K34" t="n">
-        <v>9.630000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="L34" t="n">
         <v>2.52</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>15.74</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43948</v>
+        <v>43949</v>
       </c>
       <c r="H35" t="n">
-        <v>770.2</v>
+        <v>777.2</v>
       </c>
       <c r="I35" t="n">
         <v>775.8622076514696</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.04</v>
+        <v>-4.98</v>
       </c>
       <c r="L35" t="n">
         <v>7.93</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>14.63</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44011</v>
+        <v>44012</v>
       </c>
       <c r="H36" t="n">
-        <v>692.4</v>
+        <v>686</v>
       </c>
       <c r="I36" t="n">
         <v>687.2185089904735</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K36" t="n">
-        <v>-10.91</v>
+        <v>-11.73</v>
       </c>
       <c r="L36" t="n">
         <v>14.44</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44061</v>
+        <v>44062</v>
       </c>
       <c r="H37" t="n">
-        <v>705.6</v>
+        <v>724.8</v>
       </c>
       <c r="I37" t="n">
         <v>707.5049655068402</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.86</v>
+        <v>-5.66</v>
       </c>
       <c r="L37" t="n">
-        <v>5.92</v>
+        <v>7.38</v>
       </c>
       <c r="M37" t="n">
         <v>1.01</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H38" t="n">
-        <v>858.1</v>
+        <v>835.1</v>
       </c>
       <c r="I38" t="n">
         <v>849.6775103499149</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K38" t="n">
-        <v>18.39</v>
+        <v>15.22</v>
       </c>
       <c r="L38" t="n">
         <v>4.11</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>7</v>
+      </c>
+      <c r="U38" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>11.05</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44281</v>
+        <v>44285</v>
       </c>
       <c r="H39" t="n">
-        <v>900.2</v>
+        <v>913.2</v>
       </c>
       <c r="I39" t="n">
         <v>912.1285472411067</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.8</v>
+        <v>-9.35</v>
       </c>
       <c r="L39" t="n">
-        <v>8.67</v>
+        <v>10.07</v>
       </c>
       <c r="M39" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="N39" t="n">
         <v>2.77</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>7.18</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44302</v>
+        <v>44305</v>
       </c>
       <c r="H40" t="n">
-        <v>911.8</v>
+        <v>885.4</v>
       </c>
       <c r="I40" t="n">
         <v>887.6938086009598</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.15</v>
+        <v>-3.04</v>
       </c>
       <c r="L40" t="n">
-        <v>2.65</v>
+        <v>3.42</v>
       </c>
       <c r="M40" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="N40" t="n">
         <v>3.68</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44335</v>
+        <v>44336</v>
       </c>
       <c r="H41" t="n">
-        <v>960.5</v>
+        <v>968</v>
       </c>
       <c r="I41" t="n">
         <v>961.4094678469676</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.48</v>
+        <v>-9.33</v>
       </c>
       <c r="L41" t="n">
-        <v>9.960000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="M41" t="n">
         <v>0.83</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.01</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H42" t="n">
-        <v>1208.8</v>
+        <v>1152.8</v>
       </c>
       <c r="I42" t="n">
         <v>1179.963067468253</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K42" t="n">
-        <v>24.88</v>
+        <v>19.09</v>
       </c>
       <c r="L42" t="n">
         <v>0.74</v>
@@ -2835,7 +3338,7 @@
         <v>0.55</v>
       </c>
       <c r="N42" t="n">
-        <v>2.15</v>
+        <v>4.63</v>
       </c>
       <c r="O42" t="n">
         <v>0.78</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.69</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44543</v>
+        <v>44544</v>
       </c>
       <c r="H43" t="n">
-        <v>1179</v>
+        <v>1194.6</v>
       </c>
       <c r="I43" t="n">
         <v>1188.147996098717</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.27</v>
+        <v>-3.63</v>
       </c>
       <c r="L43" t="n">
         <v>8</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.33</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H44" t="n">
-        <v>1294.9</v>
+        <v>1230.4</v>
       </c>
       <c r="I44" t="n">
         <v>1289.486245841044</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K44" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
         <v>2.51</v>
       </c>
       <c r="M44" t="n">
-        <v>0.92</v>
+        <v>1.54</v>
       </c>
       <c r="N44" t="n">
-        <v>2.23</v>
+        <v>4.98</v>
       </c>
       <c r="O44" t="n">
         <v>1.32</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.92</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H45" t="n">
-        <v>1185.3</v>
+        <v>1231.4</v>
       </c>
       <c r="I45" t="n">
         <v>1206.916506712449</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K45" t="n">
-        <v>3.67</v>
+        <v>-0.08</v>
       </c>
       <c r="L45" t="n">
         <v>4.71</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>11.04</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H46" t="n">
-        <v>1182.2</v>
+        <v>1164.3</v>
       </c>
       <c r="I46" t="n">
         <v>1173.053267114589</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K46" t="n">
-        <v>-4</v>
+        <v>-5.45</v>
       </c>
       <c r="L46" t="n">
-        <v>5.69</v>
+        <v>6.41</v>
       </c>
       <c r="M46" t="n">
         <v>2.61</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.75</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44749</v>
+        <v>44750</v>
       </c>
       <c r="H47" t="n">
-        <v>1118.5</v>
+        <v>1125.4</v>
       </c>
       <c r="I47" t="n">
         <v>1118.548938335826</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K47" t="n">
-        <v>3.93</v>
+        <v>3.34</v>
       </c>
       <c r="L47" t="n">
         <v>5.94</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.92</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44832</v>
+        <v>44833</v>
       </c>
       <c r="H48" t="n">
-        <v>1384.9</v>
+        <v>1352.1</v>
       </c>
       <c r="I48" t="n">
         <v>1357.713426523233</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K48" t="n">
-        <v>23.06</v>
+        <v>20.14</v>
       </c>
       <c r="L48" t="n">
         <v>0.97</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44900</v>
+        <v>44901</v>
       </c>
       <c r="H49" t="n">
-        <v>1366.9</v>
+        <v>1378.6</v>
       </c>
       <c r="I49" t="n">
         <v>1376.059530504194</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.09</v>
+        <v>-1.96</v>
       </c>
       <c r="L49" t="n">
         <v>3.1</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>5.64</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44909</v>
+        <v>44910</v>
       </c>
       <c r="H50" t="n">
-        <v>1318.2</v>
+        <v>1308.3</v>
       </c>
       <c r="I50" t="n">
         <v>1317.670021636803</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.38</v>
+        <v>-5.1</v>
       </c>
       <c r="L50" t="n">
-        <v>4.85</v>
+        <v>5.4</v>
       </c>
       <c r="M50" t="n">
         <v>0.36</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.62</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45033</v>
+        <v>45034</v>
       </c>
       <c r="H51" t="n">
-        <v>1184.8</v>
+        <v>1216.2</v>
       </c>
       <c r="I51" t="n">
         <v>1196.774169768693</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K51" t="n">
-        <v>9.44</v>
+        <v>7.04</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -3348,7 +3959,7 @@
         <v>0.96</v>
       </c>
       <c r="N51" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="O51" t="n">
         <v>-0.75</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.58</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45147</v>
+        <v>45148</v>
       </c>
       <c r="H52" t="n">
-        <v>1301.8</v>
+        <v>1260</v>
       </c>
       <c r="I52" t="n">
         <v>1277.753601791712</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K52" t="n">
-        <v>7.04</v>
+        <v>3.6</v>
       </c>
       <c r="L52" t="n">
         <v>3.31</v>
@@ -3405,7 +4028,7 @@
         <v>2.27</v>
       </c>
       <c r="N52" t="n">
-        <v>1.67</v>
+        <v>3.21</v>
       </c>
       <c r="O52" t="n">
         <v>2.65</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.33</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45229</v>
+        <v>45230</v>
       </c>
       <c r="H53" t="n">
-        <v>1156.1</v>
+        <v>1229</v>
       </c>
       <c r="I53" t="n">
         <v>1206.909576713903</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K53" t="n">
-        <v>8.25</v>
+        <v>2.46</v>
       </c>
       <c r="L53" t="n">
         <v>3.93</v>
       </c>
       <c r="M53" t="n">
-        <v>1.21</v>
+        <v>2.24</v>
       </c>
       <c r="N53" t="n">
-        <v>2.7</v>
+        <v>6.31</v>
       </c>
       <c r="O53" t="n">
         <v>-3.21</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.69</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H54" t="n">
-        <v>1338.8</v>
+        <v>1261.3</v>
       </c>
       <c r="I54" t="n">
         <v>1306.509406395076</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K54" t="n">
-        <v>8.93</v>
+        <v>2.63</v>
       </c>
       <c r="L54" t="n">
         <v>4.38</v>
@@ -3519,7 +4166,7 @@
         <v>0.74</v>
       </c>
       <c r="N54" t="n">
-        <v>2.44</v>
+        <v>5.79</v>
       </c>
       <c r="O54" t="n">
         <v>6.31</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.7</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="H55" t="n">
-        <v>1355.6</v>
+        <v>1372.8</v>
       </c>
       <c r="I55" t="n">
         <v>1356.279668346208</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K55" t="n">
-        <v>-7.48</v>
+        <v>-8.84</v>
       </c>
       <c r="L55" t="n">
-        <v>8.140000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="M55" t="n">
         <v>4.26</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.09</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="H56" t="n">
-        <v>1435.9</v>
+        <v>1415.4</v>
       </c>
       <c r="I56" t="n">
         <v>1423.54233510805</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K56" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="L56" t="n">
         <v>3.12</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.43</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="H57" t="n">
-        <v>1491.2</v>
+        <v>1510.6</v>
       </c>
       <c r="I57" t="n">
         <v>1506.359277487843</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.36</v>
+        <v>-6.73</v>
       </c>
       <c r="L57" t="n">
-        <v>6.15</v>
+        <v>6.9</v>
       </c>
       <c r="M57" t="n">
         <v>0.75</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.48</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="H58" t="n">
-        <v>1475.1</v>
+        <v>1407.5</v>
       </c>
       <c r="I58" t="n">
         <v>1432.538420096325</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.35</v>
+        <v>-6.83</v>
       </c>
       <c r="L58" t="n">
-        <v>3</v>
+        <v>8.08</v>
       </c>
       <c r="M58" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>4.58</v>
       </c>
       <c r="O58" t="n">
         <v>1.3</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>10.15</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="H59" t="n">
-        <v>1531.1</v>
+        <v>1583.1</v>
       </c>
       <c r="I59" t="n">
         <v>1547.590317735589</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.779999999999999</v>
+        <v>-12.48</v>
       </c>
       <c r="L59" t="n">
-        <v>9.640000000000001</v>
+        <v>14.78</v>
       </c>
       <c r="M59" t="n">
         <v>2.2</v>
       </c>
       <c r="N59" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="O59" t="n">
         <v>-4.58</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H60" t="n">
-        <v>1604.4</v>
+        <v>1576.6</v>
       </c>
       <c r="I60" t="n">
         <v>1593.699201968559</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K60" t="n">
-        <v>1.35</v>
+        <v>-0.41</v>
       </c>
       <c r="L60" t="n">
         <v>5.27</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.99</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="H61" t="n">
-        <v>1574.5</v>
+        <v>1602.4</v>
       </c>
       <c r="I61" t="n">
         <v>1584.620546784718</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K61" t="n">
-        <v>0.13</v>
+        <v>-1.64</v>
       </c>
       <c r="L61" t="n">
         <v>4.8</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>7.74</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H62" t="n">
-        <v>1528.8</v>
+        <v>1494.5</v>
       </c>
       <c r="I62" t="n">
         <v>1504.652193312991</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.59</v>
+        <v>-6.73</v>
       </c>
       <c r="L62" t="n">
-        <v>4.8</v>
+        <v>6.94</v>
       </c>
       <c r="M62" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="N62" t="n">
         <v>3.52</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.42</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H63" t="n">
-        <v>1435.8</v>
+        <v>1473.6</v>
       </c>
       <c r="I63" t="n">
         <v>1467.611632265968</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K63" t="n">
-        <v>3.93</v>
+        <v>1.4</v>
       </c>
       <c r="L63" t="n">
         <v>1.64</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>8.56</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="H64" t="n">
-        <v>1380.9</v>
+        <v>1348.2</v>
       </c>
       <c r="I64" t="n">
         <v>1359.425110490102</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.29</v>
+        <v>-8.51</v>
       </c>
       <c r="L64" t="n">
-        <v>7.47</v>
+        <v>8.69</v>
       </c>
       <c r="M64" t="n">
         <v>1.54</v>
       </c>
       <c r="N64" t="n">
-        <v>1.29</v>
+        <v>2.37</v>
       </c>
       <c r="O64" t="n">
         <v>2.63</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="H65" t="n">
-        <v>1411.5</v>
+        <v>1422.7</v>
       </c>
       <c r="I65" t="n">
         <v>1419.616443449052</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.7</v>
+        <v>-5.53</v>
       </c>
       <c r="L65" t="n">
-        <v>6.19</v>
+        <v>8.44</v>
       </c>
       <c r="M65" t="n">
         <v>0.76</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.44</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H66" t="n">
-        <v>1482.6</v>
+        <v>1467.2</v>
       </c>
       <c r="I66" t="n">
         <v>1476.717013547042</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K66" t="n">
-        <v>4.21</v>
+        <v>3.13</v>
       </c>
       <c r="L66" t="n">
         <v>2.02</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>5.61</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="H67" t="n">
-        <v>1475.9</v>
+        <v>1498.8</v>
       </c>
       <c r="I67" t="n">
         <v>1498.051706556571</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.59</v>
+        <v>-2.15</v>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>3.18</v>
       </c>
       <c r="M67" t="n">
         <v>0.92</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>5.56</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="H68" t="n">
-        <v>1519</v>
+        <v>1489.3</v>
       </c>
       <c r="I68" t="n">
         <v>1490.779172946726</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K68" t="n">
-        <v>1.35</v>
+        <v>-0.63</v>
       </c>
       <c r="L68" t="n">
         <v>1.55</v>
@@ -4317,7 +5132,7 @@
         <v>1.3</v>
       </c>
       <c r="N68" t="n">
-        <v>1.28</v>
+        <v>1.96</v>
       </c>
       <c r="O68" t="n">
         <v>1.55</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.34</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="H69" t="n">
-        <v>1505</v>
+        <v>1514.8</v>
       </c>
       <c r="I69" t="n">
         <v>1505.051251341737</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.05</v>
+        <v>-1.71</v>
       </c>
       <c r="L69" t="n">
         <v>4.16</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>4.75</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H70" t="n">
-        <v>1474.8</v>
+        <v>1435.2</v>
       </c>
       <c r="I70" t="n">
         <v>1442.870006335696</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.64</v>
+        <v>-5.25</v>
       </c>
       <c r="L70" t="n">
-        <v>3.38</v>
+        <v>5.76</v>
       </c>
       <c r="M70" t="n">
         <v>1.12</v>
       </c>
       <c r="N70" t="n">
-        <v>1.25</v>
+        <v>2.69</v>
       </c>
       <c r="O70" t="n">
         <v>0.65</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.59</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="H71" t="n">
-        <v>1497.6</v>
+        <v>1516.9</v>
       </c>
       <c r="I71" t="n">
         <v>1504.501451803842</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.35</v>
+        <v>-5.69</v>
       </c>
       <c r="L71" t="n">
-        <v>4.93</v>
+        <v>6.26</v>
       </c>
       <c r="M71" t="n">
         <v>1.63</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>5.9</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H72" t="n">
-        <v>1433.8</v>
+        <v>1386.4</v>
       </c>
       <c r="I72" t="n">
         <v>1427.469986293797</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.48</v>
+        <v>-8.6</v>
       </c>
       <c r="L72" t="n">
-        <v>6.32</v>
+        <v>9.91</v>
       </c>
       <c r="M72" t="n">
         <v>4.16</v>
       </c>
       <c r="N72" t="n">
-        <v>1.8</v>
+        <v>3.31</v>
       </c>
       <c r="O72" t="n">
         <v>1.29</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.4</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H73" t="n">
-        <v>1390.5</v>
+        <v>1407.8</v>
       </c>
       <c r="I73" t="n">
         <v>1404.748918164869</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.3</v>
+        <v>-1.54</v>
       </c>
       <c r="L73" t="n">
         <v>3.77</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.6</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H74" t="n">
-        <v>1629.5</v>
+        <v>1575</v>
       </c>
       <c r="I74" t="n">
         <v>1601.185824610568</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K74" t="n">
-        <v>15.75</v>
+        <v>11.88</v>
       </c>
       <c r="L74" t="n">
         <v>4.27</v>
@@ -4659,7 +5546,7 @@
         <v>1.87</v>
       </c>
       <c r="N74" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="O74" t="n">
         <v>1.24</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>6</v>
+      </c>
+      <c r="U74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>35</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9677,7 +10584,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="6">
@@ -9687,7 +10594,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9697,7 +10604,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
@@ -9707,7 +10614,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -9717,7 +10624,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -9727,7 +10634,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120.2</v>
+        <v>122.8</v>
       </c>
     </row>
     <row r="11">
@@ -9737,7 +10644,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -9747,7 +10654,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -9757,7 +10664,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.9</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="14">
@@ -9767,7 +10674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.16</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="15">
@@ -9777,7 +10684,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.54</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="16">
@@ -9787,7 +10694,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.3</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="17">
@@ -9797,7 +10704,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33.78</v>
+        <v>31.69</v>
       </c>
     </row>
     <row r="18">
@@ -9807,7 +10714,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="19">
@@ -9817,7 +10724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.25</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="20">
@@ -9827,7 +10734,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.53</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="21">
@@ -9837,7 +10744,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.44</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="22">
@@ -9847,7 +10754,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -9857,7 +10764,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -9867,7 +10774,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="25">
@@ -9887,7 +10794,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.19</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="27">
@@ -9897,7 +10804,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.05</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="28">
@@ -9907,7 +10814,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
